--- a/outputs/q4/summary.xlsx
+++ b/outputs/q4/summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>49972.16388888888</v>
+        <v>35653.96006470839</v>
       </c>
     </row>
     <row r="4">
@@ -467,7 +467,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>21772.16388888888</v>
+        <v>7453.960064708386</v>
       </c>
     </row>
     <row r="5">
@@ -477,7 +477,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7720625492513788</v>
+        <v>0.264324824989659</v>
       </c>
     </row>
     <row r="6">
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>99944.32777777777</v>
+        <v>71307.92012941677</v>
       </c>
     </row>
     <row r="7">
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1281743.81493482</v>
+        <v>671221.8689317798</v>
       </c>
     </row>
     <row r="8">
@@ -507,7 +507,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>102294.2731529621</v>
+        <v>75495.42500039333</v>
       </c>
     </row>
     <row r="9">
@@ -517,7 +517,47 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>812832.0000000002</v>
+        <v>588085.5399541908</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>预测周供货能力最小值</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>23344.09234378129</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>预测周供货能力最大值</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>27347.65691565125</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>周发运量最小值</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>23344.09234378129</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>周发运量最大值</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>26003.07235849818</v>
       </c>
     </row>
   </sheetData>
